--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/AssetInfoDetailRisk.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/AssetInfoDetailRisk.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD12442-9DAF-44A2-AFE6-1FA134B21C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC347DA-B130-4DB1-9C8E-2633A3505F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="产品基本信息" sheetId="5" r:id="rId1"/>
+    <sheet name="资产要素信息" sheetId="5" r:id="rId1"/>
     <sheet name="填写说明" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
